--- a/backend/data/golden_set/review/jd_manual_review_round1.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round1.xlsx
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>["Python","C++","大语言模型","LoRA","增量预训练","模型对齐","PyTorch","DeepSpeed","Megatron","vLLM","TensorRT-LLM","模型量化","模型部署"]</t>
+          <t>["Python", "C++", "大语言模型", "LoRA", "增量预训练", "模型对齐", "PyTorch", "DeepSpeed", "Megatron", "vLLM", "TensorRT-LLM", "模型量化", "模型部署", "自然语言处理", "语音交互", "计算机视觉", "深度学习", "DeepSeek", "Qwen"]</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>["HTML","JavaScript","CSS","AngularJS","jQuery","Linux","Scala","Python","Shell","Perl","Hadoop","HBase","Flume","Kafka","Flink","Hive","Spark"]</t>
+          <t>["Linux", "Scala", "Python", "Shell", "Perl", "Hadoop", "HBase", "Flume", "Kafka", "Flink", "Hive", "Spark", "需求分析", "数据分析", "项目管理"]</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
